--- a/output/pdf_financials_xlsx/NT.xlsx
+++ b/output/pdf_financials_xlsx/NT.xlsx
@@ -1918,13 +1918,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.040511</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.066099</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.066099</v>
       </c>
     </row>
     <row r="93">
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>-0.019124</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="D118" s="3" t="n">
         <v>0</v>
@@ -3015,7 +3015,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" s="5" t="n">
         <v>0.040511</v>
       </c>
@@ -3385,7 +3389,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E24" s="5" t="n">
         <v>-0.019124</v>
       </c>

--- a/output/pdf_financials_xlsx/NT.xlsx
+++ b/output/pdf_financials_xlsx/NT.xlsx
@@ -978,13 +978,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.046946</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.051691</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.020268</v>
       </c>
     </row>
     <row r="35">
@@ -1010,13 +1010,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.046946</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.051691</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.020268</v>
       </c>
     </row>
     <row r="37">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.046946</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.082487</v>
+        <v>0.030796</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.045268</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="49">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/NT.xlsx
+++ b/output/pdf_financials_xlsx/NT.xlsx
@@ -2053,13 +2053,13 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.008506</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>0.002066</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>0.012822</v>
       </c>
     </row>
     <row r="102">
@@ -2133,13 +2133,13 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.042124</v>
+        <v>0.033618</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>-0.115993</v>
+        <v>-0.113927</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.005953</v>
+        <v>0.018775</v>
       </c>
     </row>
     <row r="107">
@@ -3265,7 +3265,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E20" s="5" t="n">
         <v>-0.008506</v>
       </c>
